--- a/data/base/Backlog_28.xlsx
+++ b/data/base/Backlog_28.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franciscoj\Python_Initial\Pyhton_Web\data\base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{4DC07E58-A16E-4E0A-851B-64FAD4A0D54B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2D5379D-AD14-4965-B81F-4D5B85DAF337}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{79A1B58E-1454-4B78-95CE-A801F35A845E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{79A1B58E-1454-4B78-95CE-A801F35A845E}"/>
   </bookViews>
   <sheets>
     <sheet name="ITI" sheetId="1" r:id="rId1"/>
@@ -20,12 +20,25 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ITI!$A$1:$K$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">SPN!$A$1:$K$1</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="32">
   <si>
     <t>Status</t>
   </si>
@@ -118,6 +131,9 @@
   </si>
   <si>
     <t>Willian Rios</t>
+  </si>
+  <si>
+    <t>Resolvido</t>
   </si>
 </sst>
 </file>
@@ -273,7 +289,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -456,6 +472,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -635,7 +657,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -643,21 +665,22 @@
     <xf numFmtId="0" fontId="18" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="34" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="17" fontId="0" fillId="34" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Ênfase1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1084,14 +1107,14 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:11" s="8" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="7" t="s">
         <v>27</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="7">
         <v>2026</v>
       </c>
       <c r="D2" s="4">
@@ -1106,27 +1129,27 @@
       <c r="G2" s="4">
         <v>20935</v>
       </c>
-      <c r="H2" s="7">
+      <c r="H2" s="6">
         <v>46204</v>
       </c>
       <c r="I2" s="5">
         <v>46223</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K2" s="7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" s="8" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="7" t="s">
         <v>27</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="7">
         <v>2026</v>
       </c>
       <c r="D3" s="4">
@@ -1141,7 +1164,7 @@
       <c r="G3" s="4">
         <v>20963</v>
       </c>
-      <c r="H3" s="7">
+      <c r="H3" s="6">
         <v>46204</v>
       </c>
       <c r="I3" s="5">
@@ -1150,18 +1173,18 @@
       <c r="J3" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="K3" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+      <c r="K3" s="7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" s="8" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="7" t="s">
         <v>27</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="7">
         <v>2026</v>
       </c>
       <c r="D4" s="4">
@@ -1176,27 +1199,27 @@
       <c r="G4" s="4">
         <v>20965</v>
       </c>
-      <c r="H4" s="7">
+      <c r="H4" s="6">
         <v>46204</v>
       </c>
       <c r="I4" s="5">
         <v>46223</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K4" s="7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" s="8" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
         <v>27</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="7">
         <v>2026</v>
       </c>
       <c r="D5" s="4">
@@ -1211,27 +1234,27 @@
       <c r="G5" s="4">
         <v>20968</v>
       </c>
-      <c r="H5" s="7">
+      <c r="H5" s="6">
         <v>46204</v>
       </c>
       <c r="I5" s="5">
         <v>46223</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" s="8" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="7" t="s">
         <v>27</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="7">
         <v>2026</v>
       </c>
       <c r="D6" s="4">
@@ -1246,7 +1269,7 @@
       <c r="G6" s="4">
         <v>20970</v>
       </c>
-      <c r="H6" s="7">
+      <c r="H6" s="6">
         <v>46204</v>
       </c>
       <c r="I6" s="5">
@@ -1255,18 +1278,18 @@
       <c r="J6" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="K6" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
+      <c r="K6" s="7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" s="8" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
         <v>27</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="7">
         <v>2026</v>
       </c>
       <c r="D7" s="4">
@@ -1281,27 +1304,27 @@
       <c r="G7" s="4">
         <v>21007</v>
       </c>
-      <c r="H7" s="7">
+      <c r="H7" s="6">
         <v>46204</v>
       </c>
       <c r="I7" s="5">
         <v>46223</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K7" s="7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" s="8" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="7" t="s">
         <v>27</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" s="7">
         <v>2026</v>
       </c>
       <c r="D8" s="4">
@@ -1316,27 +1339,27 @@
       <c r="G8" s="4">
         <v>21108</v>
       </c>
-      <c r="H8" s="7">
+      <c r="H8" s="6">
         <v>46204</v>
       </c>
       <c r="I8" s="5">
         <v>46223</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K8" s="7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" s="8" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
         <v>27</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9" s="7">
         <v>2026</v>
       </c>
       <c r="D9" s="4">
@@ -1351,27 +1374,27 @@
       <c r="G9" s="4">
         <v>21151</v>
       </c>
-      <c r="H9" s="7">
+      <c r="H9" s="6">
         <v>46204</v>
       </c>
       <c r="I9" s="5">
         <v>46223</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K9" s="7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" s="8" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="7" t="s">
         <v>27</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="7">
         <v>2026</v>
       </c>
       <c r="D10" s="4">
@@ -1386,27 +1409,27 @@
       <c r="G10" s="4">
         <v>21210</v>
       </c>
-      <c r="H10" s="7">
+      <c r="H10" s="6">
         <v>46204</v>
       </c>
       <c r="I10" s="5">
         <v>46223</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K10" s="7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" s="8" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
         <v>27</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11" s="7">
         <v>2026</v>
       </c>
       <c r="D11" s="4">
@@ -1421,27 +1444,27 @@
       <c r="G11" s="4">
         <v>21144</v>
       </c>
-      <c r="H11" s="7">
+      <c r="H11" s="6">
         <v>46204</v>
       </c>
       <c r="I11" s="5">
         <v>46223</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K11" s="7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" s="8" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="7" t="s">
         <v>27</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="7">
         <v>2026</v>
       </c>
       <c r="D12" s="4">
@@ -1456,7 +1479,7 @@
       <c r="G12" s="4">
         <v>20486</v>
       </c>
-      <c r="H12" s="7">
+      <c r="H12" s="6">
         <v>46204</v>
       </c>
       <c r="I12" s="5">
@@ -1465,18 +1488,18 @@
       <c r="J12" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="K12" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
+      <c r="K12" s="7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" s="8" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
         <v>27</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C13" s="3">
+      <c r="C13" s="7">
         <v>2026</v>
       </c>
       <c r="D13" s="4">
@@ -1491,7 +1514,7 @@
       <c r="G13" s="4">
         <v>21208</v>
       </c>
-      <c r="H13" s="7">
+      <c r="H13" s="6">
         <v>46204</v>
       </c>
       <c r="I13" s="5">
@@ -1500,18 +1523,18 @@
       <c r="J13" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="K13" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
+      <c r="K13" s="7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" s="8" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="7" t="s">
         <v>27</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C14" s="3">
+      <c r="C14" s="7">
         <v>2026</v>
       </c>
       <c r="D14" s="4">
@@ -1526,7 +1549,7 @@
       <c r="G14" s="4">
         <v>21298</v>
       </c>
-      <c r="H14" s="7">
+      <c r="H14" s="6">
         <v>46204</v>
       </c>
       <c r="I14" s="5">
@@ -1535,18 +1558,18 @@
       <c r="J14" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
+      <c r="K14" s="7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" s="8" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="7" t="s">
         <v>27</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C15" s="3">
+      <c r="C15" s="7">
         <v>2026</v>
       </c>
       <c r="D15" s="4">
@@ -1561,7 +1584,7 @@
       <c r="G15" s="4">
         <v>21340</v>
       </c>
-      <c r="H15" s="7">
+      <c r="H15" s="6">
         <v>46204</v>
       </c>
       <c r="I15" s="5">
@@ -1570,18 +1593,18 @@
       <c r="J15" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="K15" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
+      <c r="K15" s="7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" s="8" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="7" t="s">
         <v>27</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C16" s="3">
+      <c r="C16" s="7">
         <v>2026</v>
       </c>
       <c r="D16" s="4">
@@ -1596,7 +1619,7 @@
       <c r="G16" s="4">
         <v>19657</v>
       </c>
-      <c r="H16" s="7">
+      <c r="H16" s="6">
         <v>46174</v>
       </c>
       <c r="I16" s="5">
@@ -1605,18 +1628,18 @@
       <c r="J16" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="K16" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
+      <c r="K16" s="7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" s="8" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="7" t="s">
         <v>27</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C17" s="3">
+      <c r="C17" s="7">
         <v>2026</v>
       </c>
       <c r="D17" s="4">
@@ -1631,7 +1654,7 @@
       <c r="G17" s="4">
         <v>20151</v>
       </c>
-      <c r="H17" s="7">
+      <c r="H17" s="6">
         <v>46204</v>
       </c>
       <c r="I17" s="5">
@@ -1640,18 +1663,18 @@
       <c r="J17" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
+      <c r="K17" s="7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" s="8" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="7" t="s">
         <v>27</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C18" s="3">
+      <c r="C18" s="7">
         <v>2026</v>
       </c>
       <c r="D18" s="4">
@@ -1666,7 +1689,7 @@
       <c r="G18" s="4">
         <v>20926</v>
       </c>
-      <c r="H18" s="7">
+      <c r="H18" s="6">
         <v>46204</v>
       </c>
       <c r="I18" s="5">
@@ -1675,18 +1698,18 @@
       <c r="J18" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
+      <c r="K18" s="7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" s="8" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="7" t="s">
         <v>27</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C19" s="3">
+      <c r="C19" s="7">
         <v>2026</v>
       </c>
       <c r="D19" s="4">
@@ -1701,7 +1724,7 @@
       <c r="G19" s="4">
         <v>21389</v>
       </c>
-      <c r="H19" s="7">
+      <c r="H19" s="6">
         <v>46204</v>
       </c>
       <c r="I19" s="5">
@@ -1710,18 +1733,18 @@
       <c r="J19" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="K19" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
+      <c r="K19" s="7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" s="8" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A20" s="7" t="s">
         <v>27</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C20" s="3">
+      <c r="C20" s="7">
         <v>2026</v>
       </c>
       <c r="D20" s="4">
@@ -1736,7 +1759,7 @@
       <c r="G20" s="4">
         <v>20874</v>
       </c>
-      <c r="H20" s="7">
+      <c r="H20" s="6">
         <v>46204</v>
       </c>
       <c r="I20" s="5">
@@ -1745,18 +1768,18 @@
       <c r="J20" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
+      <c r="K20" s="7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" s="8" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A21" s="7" t="s">
         <v>27</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C21" s="3">
+      <c r="C21" s="7">
         <v>2026</v>
       </c>
       <c r="D21" s="4">
@@ -1771,7 +1794,7 @@
       <c r="G21" s="4">
         <v>20268</v>
       </c>
-      <c r="H21" s="7">
+      <c r="H21" s="6">
         <v>46204</v>
       </c>
       <c r="I21" s="5">
@@ -1780,18 +1803,18 @@
       <c r="J21" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
+      <c r="K21" s="7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" s="8" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A22" s="7" t="s">
         <v>27</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C22" s="3">
+        <v>2</v>
+      </c>
+      <c r="C22" s="7">
         <v>2026</v>
       </c>
       <c r="D22" s="4">
@@ -1806,7 +1829,7 @@
       <c r="G22" s="4">
         <v>20776</v>
       </c>
-      <c r="H22" s="7">
+      <c r="H22" s="6">
         <v>46204</v>
       </c>
       <c r="I22" s="5">
@@ -1815,18 +1838,18 @@
       <c r="J22" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
+      <c r="K22" s="7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" s="8" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A23" s="7" t="s">
         <v>27</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C23" s="3">
+      <c r="C23" s="7">
         <v>2026</v>
       </c>
       <c r="D23" s="4">
@@ -1841,7 +1864,7 @@
       <c r="G23" s="4">
         <v>20837</v>
       </c>
-      <c r="H23" s="7">
+      <c r="H23" s="6">
         <v>46204</v>
       </c>
       <c r="I23" s="5">
@@ -1850,18 +1873,18 @@
       <c r="J23" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="K23" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
+      <c r="K23" s="7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" s="8" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A24" s="7" t="s">
         <v>27</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C24" s="3">
+      <c r="C24" s="7">
         <v>2026</v>
       </c>
       <c r="D24" s="4">
@@ -1876,7 +1899,7 @@
       <c r="G24" s="4">
         <v>20873</v>
       </c>
-      <c r="H24" s="7">
+      <c r="H24" s="6">
         <v>46204</v>
       </c>
       <c r="I24" s="5">
@@ -1885,18 +1908,18 @@
       <c r="J24" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
+      <c r="K24" s="7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" s="8" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A25" s="7" t="s">
         <v>27</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C25" s="3">
+      <c r="C25" s="7">
         <v>2026</v>
       </c>
       <c r="D25" s="4">
@@ -1911,27 +1934,27 @@
       <c r="G25" s="4">
         <v>20769</v>
       </c>
-      <c r="H25" s="7">
+      <c r="H25" s="6">
         <v>46204</v>
       </c>
       <c r="I25" s="5">
         <v>46223</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="K25" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A26" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K25" s="7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" s="8" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A26" s="7" t="s">
         <v>27</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C26" s="3">
+      <c r="C26" s="7">
         <v>2026</v>
       </c>
       <c r="D26" s="4">
@@ -1946,7 +1969,7 @@
       <c r="G26" s="4">
         <v>21202</v>
       </c>
-      <c r="H26" s="7">
+      <c r="H26" s="6">
         <v>46204</v>
       </c>
       <c r="I26" s="5">
@@ -1955,18 +1978,18 @@
       <c r="J26" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A27" s="3" t="s">
+      <c r="K26" s="7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" s="8" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A27" s="7" t="s">
         <v>27</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C27" s="3">
+      <c r="C27" s="7">
         <v>2026</v>
       </c>
       <c r="D27" s="4">
@@ -1981,7 +2004,7 @@
       <c r="G27" s="4">
         <v>19631</v>
       </c>
-      <c r="H27" s="7">
+      <c r="H27" s="6">
         <v>46174</v>
       </c>
       <c r="I27" s="5">
@@ -1990,18 +2013,18 @@
       <c r="J27" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
+      <c r="K27" s="7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" s="8" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A28" s="7" t="s">
         <v>27</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C28" s="3">
+      <c r="C28" s="7">
         <v>2026</v>
       </c>
       <c r="D28" s="4">
@@ -2016,27 +2039,27 @@
       <c r="G28" s="4">
         <v>20482</v>
       </c>
-      <c r="H28" s="7">
+      <c r="H28" s="6">
         <v>46204</v>
       </c>
       <c r="I28" s="5">
         <v>46223</v>
       </c>
       <c r="J28" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="K28" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A29" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K28" s="7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" s="8" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A29" s="7" t="s">
         <v>27</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C29" s="3">
+      <c r="C29" s="7">
         <v>2026</v>
       </c>
       <c r="D29" s="4">
@@ -2051,16 +2074,16 @@
       <c r="G29" s="4">
         <v>21162</v>
       </c>
-      <c r="H29" s="7">
+      <c r="H29" s="6">
         <v>46204</v>
       </c>
       <c r="I29" s="5">
         <v>46223</v>
       </c>
       <c r="J29" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="K29" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K29" s="7" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2088,7 +2111,7 @@
     <col min="7" max="7" width="11.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9.140625" style="1"/>
     <col min="9" max="9" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="15.140625" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2127,7 +2150,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" s="8" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>29</v>
       </c>
@@ -2149,20 +2172,20 @@
       <c r="G2" s="4">
         <v>21224</v>
       </c>
-      <c r="H2" s="7">
+      <c r="H2" s="6">
         <v>46204</v>
       </c>
       <c r="I2" s="5">
         <v>46223</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="K2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K2" s="7" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" s="8" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>29</v>
       </c>
@@ -2184,20 +2207,20 @@
       <c r="G3" s="4">
         <v>21229</v>
       </c>
-      <c r="H3" s="7">
+      <c r="H3" s="6">
         <v>46204</v>
       </c>
       <c r="I3" s="5">
         <v>46223</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="K3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K3" s="7" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" s="8" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>29</v>
       </c>
@@ -2219,7 +2242,7 @@
       <c r="G4" s="4">
         <v>21058</v>
       </c>
-      <c r="H4" s="7">
+      <c r="H4" s="6">
         <v>46204</v>
       </c>
       <c r="I4" s="5">
@@ -2228,11 +2251,11 @@
       <c r="J4" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="K4" s="3" t="s">
+      <c r="K4" s="7" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" s="8" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>29</v>
       </c>
@@ -2254,20 +2277,20 @@
       <c r="G5" s="4">
         <v>20495</v>
       </c>
-      <c r="H5" s="7">
+      <c r="H5" s="6">
         <v>46204</v>
       </c>
       <c r="I5" s="5">
         <v>46223</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="K5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K5" s="7" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" s="8" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>29</v>
       </c>
@@ -2289,20 +2312,20 @@
       <c r="G6" s="4">
         <v>20586</v>
       </c>
-      <c r="H6" s="7">
+      <c r="H6" s="6">
         <v>46204</v>
       </c>
       <c r="I6" s="5">
         <v>46223</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="K6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K6" s="7" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" s="8" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>29</v>
       </c>
@@ -2324,20 +2347,20 @@
       <c r="G7" s="4">
         <v>20623</v>
       </c>
-      <c r="H7" s="7">
+      <c r="H7" s="6">
         <v>46204</v>
       </c>
       <c r="I7" s="5">
         <v>46223</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="K7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K7" s="7" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" s="8" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>29</v>
       </c>
@@ -2359,20 +2382,20 @@
       <c r="G8" s="4">
         <v>20820</v>
       </c>
-      <c r="H8" s="7">
+      <c r="H8" s="6">
         <v>46204</v>
       </c>
       <c r="I8" s="5">
         <v>46223</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="K8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K8" s="7" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" s="8" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>29</v>
       </c>
@@ -2394,20 +2417,20 @@
       <c r="G9" s="4">
         <v>21287</v>
       </c>
-      <c r="H9" s="7">
+      <c r="H9" s="6">
         <v>46204</v>
       </c>
       <c r="I9" s="5">
         <v>46223</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="K9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K9" s="7" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" s="8" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>29</v>
       </c>
@@ -2429,38 +2452,38 @@
       <c r="G10" s="4">
         <v>21177</v>
       </c>
-      <c r="H10" s="7">
+      <c r="H10" s="6">
         <v>46204</v>
       </c>
       <c r="I10" s="5">
         <v>46223</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="K10" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K10" s="7" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:K1" xr:uid="{0F096439-290B-4079-BB3A-F305AD580E67}">
